--- a/data/trans_orig/Q4504_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124102</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>168974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166602</t>
+          <t>167043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219285</t>
+          <t>218317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306279</t>
+          <t>303036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372417</t>
+          <t>369611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112859</t>
+          <t>113048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155807</t>
+          <t>154716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108419</t>
+          <t>107752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149797</t>
+          <t>149757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232057</t>
+          <t>228588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291302</t>
+          <t>292478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181439</t>
+          <t>184328</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234423</t>
+          <t>236128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>190255</t>
+          <t>188792</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>241747</t>
+          <t>243253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>389476</t>
+          <t>387284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>457326</t>
+          <t>458860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72753</t>
+          <t>73111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110833</t>
+          <t>110140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154779</t>
+          <t>156638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196205</t>
+          <t>195398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248565</t>
+          <t>252456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425830</t>
+          <t>421665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488408</t>
+          <t>486306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>613213</t>
+          <t>612004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>684156</t>
+          <t>683933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1056667</t>
+          <t>1056281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152035</t>
+          <t>1150600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229262</t>
+          <t>230537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291097</t>
+          <t>292545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>255350</t>
+          <t>254770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317653</t>
+          <t>317679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>501507</t>
+          <t>502771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>590192</t>
+          <t>587839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>368469</t>
+          <t>365963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>433397</t>
+          <t>432076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>336554</t>
+          <t>334558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404950</t>
+          <t>401722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>721057</t>
+          <t>719638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>816304</t>
+          <t>814699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>540141</t>
+          <t>538494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>620014</t>
+          <t>618177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>473060</t>
+          <t>472405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>548057</t>
+          <t>545523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1035492</t>
+          <t>1035971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1134154</t>
+          <t>1145499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116371</t>
+          <t>115314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163315</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>104056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149723</t>
+          <t>148226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233415</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298170</t>
+          <t>295296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284119</t>
+          <t>284410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349651</t>
+          <t>351163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263098</t>
+          <t>262155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324490</t>
+          <t>324008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566002</t>
+          <t>567458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>655231</t>
+          <t>654169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115658</t>
+          <t>113818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158332</t>
+          <t>156435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102478</t>
+          <t>104605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140301</t>
+          <t>142880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228891</t>
+          <t>227605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284279</t>
+          <t>288553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146039</t>
+          <t>141810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188436</t>
+          <t>185600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113888</t>
+          <t>113774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153229</t>
+          <t>152248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268992</t>
+          <t>267729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327058</t>
+          <t>327268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132004</t>
+          <t>136491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176874</t>
+          <t>178089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119876</t>
+          <t>121117</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160151</t>
+          <t>160368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>266081</t>
+          <t>267785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>325615</t>
+          <t>326312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>24034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47931</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72896</t>
+          <t>71240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47841</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>77006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79570</t>
+          <t>77940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105721</t>
+          <t>105381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146674</t>
+          <t>148390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>497255</t>
+          <t>500729</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>584212</t>
+          <t>582085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>554898</t>
+          <t>555915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>648036</t>
+          <t>643931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1076116</t>
+          <t>1071540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1203578</t>
+          <t>1198878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>651973</t>
+          <t>647740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>746797</t>
+          <t>744516</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>585760</t>
+          <t>582263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672713</t>
+          <t>673790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1263679</t>
+          <t>1262716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1405563</t>
+          <t>1389345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>894400</t>
+          <t>893390</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1000849</t>
+          <t>995254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>820209</t>
+          <t>814692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>916763</t>
+          <t>914552</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1741004</t>
+          <t>1733784</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1878366</t>
+          <t>1887929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231456</t>
+          <t>231226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>295824</t>
+          <t>292313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>247858</t>
+          <t>250591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>309786</t>
+          <t>311091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>494825</t>
+          <t>492873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>583761</t>
+          <t>586664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>787668</t>
+          <t>783087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>887930</t>
+          <t>886949</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>951819</t>
+          <t>948067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1058618</t>
+          <t>1055643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1766225</t>
+          <t>1763865</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1915202</t>
+          <t>1914416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166440</t>
+          <t>164881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218180</t>
+          <t>218504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197614</t>
+          <t>196924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252468</t>
+          <t>250714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380335</t>
+          <t>373234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455820</t>
+          <t>450370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>114425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159874</t>
+          <t>160274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166431</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218639</t>
+          <t>218932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296769</t>
+          <t>297229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>363137</t>
+          <t>364622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135040</t>
+          <t>134494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>183061</t>
+          <t>181304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>190064</t>
+          <t>187985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244451</t>
+          <t>244144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338620</t>
+          <t>337204</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>411554</t>
+          <t>411254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53032</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55958</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>88195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91386</t>
+          <t>91492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132592</t>
+          <t>134116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417245</t>
+          <t>415873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482293</t>
+          <t>478144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>595571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>670230</t>
+          <t>671219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1033236</t>
+          <t>1030896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1134831</t>
+          <t>1127218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>487313</t>
+          <t>490920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>568211</t>
+          <t>573160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>434172</t>
+          <t>435372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>509563</t>
+          <t>512085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>950983</t>
+          <t>945681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1054736</t>
+          <t>1062398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410361</t>
+          <t>417298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487275</t>
+          <t>492791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441217</t>
+          <t>439652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518651</t>
+          <t>520501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>875987</t>
+          <t>879443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>984186</t>
+          <t>990141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>363071</t>
+          <t>365689</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>439397</t>
+          <t>437646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>317227</t>
+          <t>318951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>384249</t>
+          <t>385951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>697220</t>
+          <t>700830</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>800418</t>
+          <t>798162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75167</t>
+          <t>77060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114616</t>
+          <t>116272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>55880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90081</t>
+          <t>90598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139247</t>
+          <t>136865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191418</t>
+          <t>189653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>447001</t>
+          <t>445041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>528019</t>
+          <t>524345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345394</t>
+          <t>345742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414528</t>
+          <t>415791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814028</t>
+          <t>810156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>922740</t>
+          <t>918158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135723</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179652</t>
+          <t>179227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157556</t>
+          <t>158990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200761</t>
+          <t>202235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305485</t>
+          <t>305845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>371588</t>
+          <t>367889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135016</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180791</t>
+          <t>179386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110240</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149481</t>
+          <t>149353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257730</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318685</t>
+          <t>314969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76964</t>
+          <t>74558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113392</t>
+          <t>111022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55729</t>
+          <t>57188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>91488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142037</t>
+          <t>139762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>191708</t>
+          <t>190817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50159</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80173</t>
+          <t>80839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83962</t>
+          <t>82049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109531</t>
+          <t>110346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153391</t>
+          <t>153397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>829228</t>
+          <t>825862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>932351</t>
+          <t>926344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>826902</t>
+          <t>827096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>931097</t>
+          <t>930182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1680732</t>
+          <t>1682076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1828048</t>
+          <t>1839316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>691540</t>
+          <t>693500</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>796909</t>
+          <t>798104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>753311</t>
+          <t>754608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>850205</t>
+          <t>848197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1477220</t>
+          <t>1470825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1617581</t>
+          <t>1617015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>600072</t>
+          <t>609818</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>697187</t>
+          <t>707142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>587881</t>
+          <t>590545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>682275</t>
+          <t>683030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1218224</t>
+          <t>1222155</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1349305</t>
+          <t>1355324</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119790</t>
+          <t>120307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168886</t>
+          <t>167534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128057</t>
+          <t>126552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176135</t>
+          <t>174268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>261835</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>328799</t>
+          <t>331548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>944262</t>
+          <t>945034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1051078</t>
+          <t>1050288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1017905</t>
+          <t>1024210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1135423</t>
+          <t>1135084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2001547</t>
+          <t>1996214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2152239</t>
+          <t>2152109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63016</t>
+          <t>60986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94634</t>
+          <t>95425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94933</t>
+          <t>96205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137132</t>
+          <t>139750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,47 +6700,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>193877</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>166943</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>223207</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>193877</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>167257</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>221540</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139854</t>
+          <t>139025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182541</t>
+          <t>183823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195277</t>
+          <t>197909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251315</t>
+          <t>252409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348201</t>
+          <t>348436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>418043</t>
+          <t>418246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87375</t>
+          <t>87502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126555</t>
+          <t>126607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,82 +6891,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>121996</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>101943</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>144857</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>228372</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>202451</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>258513</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>11,61%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121996</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>102184</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145173</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>228372</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>200384</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>257007</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67803</t>
+          <t>68127</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53453</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85530</t>
+          <t>83362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99819</t>
+          <t>101646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142717</t>
+          <t>144812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329285</t>
+          <t>327745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381510</t>
+          <t>381057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433399</t>
+          <t>433105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496353</t>
+          <t>497931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>775929</t>
+          <t>778345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>862325</t>
+          <t>862446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428237</t>
+          <t>428102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>505912</t>
+          <t>506750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>486095</t>
+          <t>488257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>565440</t>
+          <t>563762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>936036</t>
+          <t>939747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1046694</t>
+          <t>1050198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>673304</t>
+          <t>672414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>762300</t>
+          <t>761910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676473</t>
+          <t>679782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>761501</t>
+          <t>761717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375849</t>
+          <t>1373583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1501608</t>
+          <t>1497291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321515</t>
+          <t>318446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>392836</t>
+          <t>392341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310010</t>
+          <t>311870</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>377810</t>
+          <t>377592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>649805</t>
+          <t>651385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>749871</t>
+          <t>752212</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>74396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114325</t>
+          <t>112836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66603</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101369</t>
+          <t>104287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151406</t>
+          <t>153053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204558</t>
+          <t>205307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>396366</t>
+          <t>398379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475307</t>
+          <t>474790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273954</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>340224</t>
+          <t>345165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694692</t>
+          <t>688594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>795422</t>
+          <t>786624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153253</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198978</t>
+          <t>200548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208924</t>
+          <t>203692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255312</t>
+          <t>252791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373127</t>
+          <t>375594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>440678</t>
+          <t>440848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159015</t>
+          <t>159799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204677</t>
+          <t>204853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150400</t>
+          <t>150536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194081</t>
+          <t>197645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323554</t>
+          <t>317620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384787</t>
+          <t>382660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115335</t>
+          <t>115178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49227</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77652</t>
+          <t>79772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>134241</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182185</t>
+          <t>182065</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31814</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>29649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92536</t>
+          <t>91541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>47318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>78326</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113775</t>
+          <t>112633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161109</t>
+          <t>156555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>674412</t>
+          <t>674249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>773446</t>
+          <t>770773</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>824390</t>
+          <t>820864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>929069</t>
+          <t>929148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1524821</t>
+          <t>1518960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1660686</t>
+          <t>1670838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1005755</t>
+          <t>1006234</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1116383</t>
+          <t>1119697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1058507</t>
+          <t>1055424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1167681</t>
+          <t>1168503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2096988</t>
+          <t>2090949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2249539</t>
+          <t>2250037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>517503</t>
+          <t>512265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>605938</t>
+          <t>604273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>481647</t>
+          <t>488055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>567702</t>
+          <t>568352</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1023106</t>
+          <t>1027024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1147100</t>
+          <t>1150194</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141937</t>
+          <t>142053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193529</t>
+          <t>194499</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148722</t>
+          <t>147643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201845</t>
+          <t>201659</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>307280</t>
+          <t>304284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>375201</t>
+          <t>381444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>813083</t>
+          <t>808465</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913155</t>
+          <t>911516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>783237</t>
+          <t>782246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>882741</t>
+          <t>884940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1624509</t>
+          <t>1627548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1769123</t>
+          <t>1767725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4504_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124755</t>
+          <t>125357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168974</t>
+          <t>170801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>167043</t>
+          <t>167027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218317</t>
+          <t>216202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303036</t>
+          <t>301073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>369611</t>
+          <t>371189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113048</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154716</t>
+          <t>156057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107752</t>
+          <t>107962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149757</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228588</t>
+          <t>232800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>292478</t>
+          <t>293628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>184328</t>
+          <t>181094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236128</t>
+          <t>233408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>188792</t>
+          <t>189682</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>243253</t>
+          <t>243126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>387284</t>
+          <t>387876</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458860</t>
+          <t>465389</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73111</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106833</t>
+          <t>105421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110140</t>
+          <t>112354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156638</t>
+          <t>155894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,47 +1121,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>221666</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>196605</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>251538</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>221666</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>195398</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>252456</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421665</t>
+          <t>425823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486306</t>
+          <t>486362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>612004</t>
+          <t>611998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>683933</t>
+          <t>681219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1056281</t>
+          <t>1054657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150600</t>
+          <t>1152950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230537</t>
+          <t>230120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292545</t>
+          <t>293950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>254770</t>
+          <t>256637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317679</t>
+          <t>319216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502771</t>
+          <t>502783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>587839</t>
+          <t>587204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365963</t>
+          <t>364842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432076</t>
+          <t>434655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334558</t>
+          <t>335382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401722</t>
+          <t>401472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>719638</t>
+          <t>725402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814699</t>
+          <t>816924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538494</t>
+          <t>541739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>618177</t>
+          <t>620278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>472405</t>
+          <t>473448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>545523</t>
+          <t>549514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1035971</t>
+          <t>1034085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1145499</t>
+          <t>1140189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115314</t>
+          <t>115026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161816</t>
+          <t>161864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104056</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148226</t>
+          <t>149833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234935</t>
+          <t>236284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295296</t>
+          <t>298028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284410</t>
+          <t>284162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351163</t>
+          <t>349124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262155</t>
+          <t>262689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324008</t>
+          <t>323862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567458</t>
+          <t>569045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>654169</t>
+          <t>656220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113818</t>
+          <t>114342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156435</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104605</t>
+          <t>102826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142880</t>
+          <t>141606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227605</t>
+          <t>228668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288553</t>
+          <t>286978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141810</t>
+          <t>144462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185600</t>
+          <t>186995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152248</t>
+          <t>154134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267729</t>
+          <t>267218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327268</t>
+          <t>326821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136491</t>
+          <t>133824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178089</t>
+          <t>177589</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>121468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160368</t>
+          <t>159924</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>267785</t>
+          <t>264075</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>326312</t>
+          <t>327847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71240</t>
+          <t>69458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>47336</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77006</t>
+          <t>77286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48424</t>
+          <t>51239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>81086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>104871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>149065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>500729</t>
+          <t>496619</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>582085</t>
+          <t>586396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555915</t>
+          <t>552905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>643931</t>
+          <t>637208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1071540</t>
+          <t>1075930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1198878</t>
+          <t>1199010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647740</t>
+          <t>655151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>744516</t>
+          <t>747585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>582263</t>
+          <t>583982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673790</t>
+          <t>674178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1262716</t>
+          <t>1263783</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1389345</t>
+          <t>1392310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>893390</t>
+          <t>892981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>995254</t>
+          <t>997209</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>814692</t>
+          <t>814872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>914552</t>
+          <t>916760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1733784</t>
+          <t>1731364</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1887929</t>
+          <t>1875539</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231226</t>
+          <t>230847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>292313</t>
+          <t>293617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250591</t>
+          <t>246548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>311091</t>
+          <t>311632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>492873</t>
+          <t>493449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>586664</t>
+          <t>580972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>783087</t>
+          <t>783577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>886949</t>
+          <t>882824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>948067</t>
+          <t>951724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1055643</t>
+          <t>1056831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1763865</t>
+          <t>1772306</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1914416</t>
+          <t>1918951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164881</t>
+          <t>165482</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218504</t>
+          <t>219974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196924</t>
+          <t>194669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250714</t>
+          <t>253326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373234</t>
+          <t>376498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>450370</t>
+          <t>457831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114425</t>
+          <t>117881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160274</t>
+          <t>163035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>168638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>218932</t>
+          <t>217921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297229</t>
+          <t>296957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>364622</t>
+          <t>367474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134494</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181304</t>
+          <t>181252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187985</t>
+          <t>189542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244144</t>
+          <t>244143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>337204</t>
+          <t>333829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>411254</t>
+          <t>412760</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>56858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88195</t>
+          <t>90303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91492</t>
+          <t>89349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415873</t>
+          <t>417543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478144</t>
+          <t>478803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595571</t>
+          <t>599164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>671219</t>
+          <t>672976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1030896</t>
+          <t>1030816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1127218</t>
+          <t>1128523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>490920</t>
+          <t>492409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>573160</t>
+          <t>571509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>435372</t>
+          <t>437136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>512085</t>
+          <t>508526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>945681</t>
+          <t>951908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1062398</t>
+          <t>1063580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417298</t>
+          <t>413075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492791</t>
+          <t>488174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439652</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520501</t>
+          <t>515337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>879443</t>
+          <t>878434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>990141</t>
+          <t>982579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>365689</t>
+          <t>363938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>437646</t>
+          <t>435161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318951</t>
+          <t>315741</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>385951</t>
+          <t>387224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>700830</t>
+          <t>704400</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>798162</t>
+          <t>807193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77060</t>
+          <t>76418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116272</t>
+          <t>113874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90598</t>
+          <t>87491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136865</t>
+          <t>140050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189653</t>
+          <t>188424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>445041</t>
+          <t>444299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524345</t>
+          <t>526939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345742</t>
+          <t>345300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415791</t>
+          <t>415515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>810156</t>
+          <t>814211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>918158</t>
+          <t>917703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134197</t>
+          <t>136562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179227</t>
+          <t>182123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158990</t>
+          <t>159132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202235</t>
+          <t>204264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305845</t>
+          <t>305751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367889</t>
+          <t>369138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135872</t>
+          <t>135809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179386</t>
+          <t>179470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>108178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149353</t>
+          <t>149178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314969</t>
+          <t>315656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74558</t>
+          <t>75540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111022</t>
+          <t>112327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>58037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91488</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,47 +5331,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>164167</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>138527</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>188221</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>20,11%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>164167</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>139762</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>190817</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80839</t>
+          <t>80088</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51209</t>
+          <t>52121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82049</t>
+          <t>82312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110346</t>
+          <t>108294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153397</t>
+          <t>153690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>825862</t>
+          <t>823182</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>926344</t>
+          <t>931314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>827096</t>
+          <t>825050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>930182</t>
+          <t>935246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1682076</t>
+          <t>1675784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1839316</t>
+          <t>1831119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>693500</t>
+          <t>695340</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>798104</t>
+          <t>793536</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>754608</t>
+          <t>750234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>848197</t>
+          <t>851522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1470825</t>
+          <t>1473578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1617015</t>
+          <t>1607732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>609818</t>
+          <t>602989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>707142</t>
+          <t>699406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>590545</t>
+          <t>590101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>683030</t>
+          <t>687155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1222155</t>
+          <t>1226364</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1355324</t>
+          <t>1351864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120307</t>
+          <t>121370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167534</t>
+          <t>170833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>127804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174268</t>
+          <t>175364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262332</t>
+          <t>261251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331548</t>
+          <t>324128</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>945034</t>
+          <t>946418</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1050288</t>
+          <t>1050437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1024210</t>
+          <t>1021737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1135084</t>
+          <t>1139833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1996214</t>
+          <t>1995742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2152109</t>
+          <t>2156571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60986</t>
+          <t>60611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95425</t>
+          <t>94714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96205</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139750</t>
+          <t>138818</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166943</t>
+          <t>169625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223207</t>
+          <t>221840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139025</t>
+          <t>137575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183823</t>
+          <t>182568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197909</t>
+          <t>192876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252409</t>
+          <t>250184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348436</t>
+          <t>342285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>418246</t>
+          <t>415417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87502</t>
+          <t>87591</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126607</t>
+          <t>125486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>102189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144857</t>
+          <t>147309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202451</t>
+          <t>202549</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258513</t>
+          <t>260625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68127</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83362</t>
+          <t>82844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101646</t>
+          <t>100265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144812</t>
+          <t>142764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>327745</t>
+          <t>325750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381057</t>
+          <t>381291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433105</t>
+          <t>434189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497931</t>
+          <t>502074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778345</t>
+          <t>777481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>862446</t>
+          <t>863736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428102</t>
+          <t>426272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>506750</t>
+          <t>506860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488257</t>
+          <t>487715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>563762</t>
+          <t>570501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>939747</t>
+          <t>938241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1050198</t>
+          <t>1048865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672414</t>
+          <t>672993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>761910</t>
+          <t>763842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>679782</t>
+          <t>677836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>761717</t>
+          <t>763801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373583</t>
+          <t>1372514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1497291</t>
+          <t>1502678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>318446</t>
+          <t>322210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>392341</t>
+          <t>395519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>311870</t>
+          <t>312237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>377592</t>
+          <t>378339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>651385</t>
+          <t>653186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>752212</t>
+          <t>749332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74396</t>
+          <t>74665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112836</t>
+          <t>112848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67814</t>
+          <t>67076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104287</t>
+          <t>106176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153053</t>
+          <t>151542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205307</t>
+          <t>204571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398379</t>
+          <t>396173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>474790</t>
+          <t>475048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>276523</t>
+          <t>270899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345165</t>
+          <t>341366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688594</t>
+          <t>691201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>786624</t>
+          <t>795509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>150314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200548</t>
+          <t>197166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203692</t>
+          <t>205402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252791</t>
+          <t>253680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>375594</t>
+          <t>374719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>440848</t>
+          <t>443488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159799</t>
+          <t>157401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204853</t>
+          <t>206160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150536</t>
+          <t>151204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197645</t>
+          <t>194249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>317620</t>
+          <t>324317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>382660</t>
+          <t>384100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>77502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115178</t>
+          <t>113255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79772</t>
+          <t>79044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134241</t>
+          <t>135718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182065</t>
+          <t>182309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>34465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>57765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91541</t>
+          <t>92319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47318</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78326</t>
+          <t>79707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112633</t>
+          <t>113857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156555</t>
+          <t>155915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>674249</t>
+          <t>670813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>770773</t>
+          <t>770542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>820864</t>
+          <t>823495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>929148</t>
+          <t>931142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1518960</t>
+          <t>1527182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1670838</t>
+          <t>1664168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1006234</t>
+          <t>1006687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1119697</t>
+          <t>1118155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1055424</t>
+          <t>1059734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1168503</t>
+          <t>1170123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2090949</t>
+          <t>2094063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2250037</t>
+          <t>2250878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>512265</t>
+          <t>515199</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>604273</t>
+          <t>605392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>488055</t>
+          <t>488404</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>568352</t>
+          <t>575974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1027024</t>
+          <t>1027035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1150194</t>
+          <t>1149705</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142053</t>
+          <t>143820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194499</t>
+          <t>193969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147643</t>
+          <t>148401</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201659</t>
+          <t>203346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>304284</t>
+          <t>302871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>381444</t>
+          <t>376984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>808465</t>
+          <t>812657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911516</t>
+          <t>914939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>782246</t>
+          <t>789310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>884940</t>
+          <t>890424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1627548</t>
+          <t>1629498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1767725</t>
+          <t>1775596</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
